--- a/ツール/賃金台帳（総額提出用）テンプレート.xlsx
+++ b/ツール/賃金台帳（総額提出用）テンプレート.xlsx
@@ -86,7 +86,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -95,20 +95,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
         <bgColor rgb="00FFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
@@ -119,8 +107,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -150,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -167,13 +161,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -189,55 +185,52 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -246,22 +239,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -629,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B61"/>
+  <dimension ref="A2:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -723,294 +716,317 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" s="6" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">　黄色のセル＝ご入力いただく欄　／　緑色のセル＝自動計算（入力不要）です。</t>
+          <t xml:space="preserve">　←この色のセルがご入力いただく欄です。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="inlineStr"/>
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　←この色のセルは自動計算です（入力不要）。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>【毎月の金額に入れるもの（重要）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>・各月の「総支給額」（基本給＋残業・役職・家族・住宅などの各種手当＋通勤手当を含む、</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>・各月の「総支給額」（基本給＋残業・役職・家族・住宅などの各種手当＋通勤手当を含む、</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">　社会保険料や税金を差し引く前の支給合計）を数字でご入力ください。</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>・給与ソフト等で各月の「課税支給合計（課税計）」が分かる場合は、そちらの方が正確です。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　その場合は「年間通勤手当」欄を空欄にしてください（二重に差し引かないため）。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>・「1ヶ月目」＝対象期間（決算期）の最初の月です。暦年の1月ではありません。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　対象期間を入力すると、各月の見出しに実際の年月が自動表示されます。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="2" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>【賞与（ボーナス）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>・毎月の欄には混ぜず、「年間賞与」欄にまとめてご入力ください。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>・入れるのは「対象期間中に支給日がある賞与」の合計です（支給日ベース。</t>
+          <t>・毎月の欄には混ぜず、「年間賞与」欄にまとめてご入力ください。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　査定の対象期間ではなく、実際に支払った日で判断してください）。</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>・入れるのは対象期間（決算期）の決算に費用計上した賞与の合計です</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="2" t="inlineStr"/>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　（経費として計上した日で判断。決算書の賞与計上額と一致させてください）。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>【年間通勤手当（非課税分）】</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>・毎月の欄に通勤手当を含めた場合は、非課税分の年間合計を必ずご記入ください。</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　（補助金のルールで非課税の通勤手当は集計から除く決まりです。空欄のままだと</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　総額が過大になり、賃上げ目標が実態より高く設定されてしまいます。金額は</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　給与ソフトの「非課税支給額」や賃金台帳の通勤手当欄でご確認いただけます）</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="3" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>・通勤手当を支給していない場合、または毎月の欄に通勤手当を含めていない場合は空欄で。</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="2" t="inlineStr"/>
-    </row>
     <row r="38">
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>【氏名について】</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="3" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>・氏名が空欄の行は集計されません。実名を書きたくない場合は「社員A」「従業員1」等の</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　仮名でも構いません（このシート自体が社外非提出のため、実名でも問題ありません）。</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="2" t="inlineStr"/>
-    </row>
     <row r="42">
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>【集計の対象になる方・ならない方】</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>・役員（取締役など）は、そもそもご記入いただかなくて結構です（補助金の集計対象外）。</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　記入した場合も、雇用形態で「役員」を選べば自動で集計から外れます。</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="3" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>・中途入社・退職・休職などで12ヶ月そろわない方は、自動で集計対象外になります</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　（補助金は「その年度に全月分の給与を受けた方」だけを数える決まりのためです）。</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>・賞与のみ支給の月（月給0円・賞与だけ支給）がある方を集計に入れたい場合は、</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　その月の欄に賞与額を記入し、同額を「年間賞与」欄から差し引いてください（重複防止）。</t>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>・賞与のみ支給の月（月給0円・賞与だけ支給）がある方も、給与の支給がない月がある方として</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　集計対象外になります（12ヶ月すべて給与の支給がある方だけを数える決まりのためです）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>・パート・アルバイトの方は「年間労働時間」を必ずご入力ください</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　（人数を正社員の労働時間に換算するために使います。未入力の間は集計に入りません）。</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>・週の労働時間が正社員より短い契約社員の方は「パート・アルバイト」を選び、</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">　年間労働時間をご入力ください（労働時間で人数換算する決まりのためです）。</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="2" t="inlineStr"/>
-    </row>
     <row r="54">
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>・パート・アルバイトの人数換算に使う「正社員の年間所定労働時間」は、計算用シート下部で</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ご確認・変更できます（初期値2080時間＝週40h×52週。自社の所定労働時間に合わせてください）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>【この様式が使えないケース（担当までご相談ください）】</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="3" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>・従業員が31名以上いる／従業員を雇用していない（役員のみの）法人／</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="3" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　直近の決算期が12ヶ月に満たない（設立初年度・決算期変更など）</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="B58" s="7" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="9" t="inlineStr">
         <is>
           <t>【重要】ご提出は「提出用シート（総額のみ）」だけをお願いします。</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="7" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>「計算用（社内控え・非提出）」シートには個人ごとの給与が含まれるため、提出先へは共有せず、</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="7" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>御社内で保管してください。（誤ってExcelの「ブック全体」をPDF化しても、計算用シートの</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="7" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>個人明細は印刷されない設定にしてあります）</t>
         </is>
@@ -1055,7 +1071,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>※このシートは社内保管用です。個人ごとの給与情報を含むため、提出先には共有しないでください。</t>
         </is>
@@ -1067,133 +1083,133 @@
           <t>対象期間（前期決算期・12ヶ月）：</t>
         </is>
       </c>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>〜</t>
         </is>
       </c>
-      <c r="F3" s="8" t="n"/>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>（例：2025/7/1 〜 2026/6/30）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11">
+      <c r="A4" s="13">
         <f>IF(OR($D$3="",$F$3=""),"⚠対象期間が未入力です（決算期の開始日と終了日をご記入ください）",IFERROR(IF(EDATE($D$3,12)-1=$F$3,"","⚠対象期間が12ヶ月ちょうどになっていません（例：2025/7/1 〜 2026/6/30）"),"⚠対象期間の日付が読み取れません（日付形式でご入力ください）"))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>■ 従業員ごとの入力（黄＝入力／緑＝自動計算）　毎月の欄＝総支給額（控除前・通勤手当込／賞与は除く）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>雇用形態</t>
         </is>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="15">
         <f>IF($D$3="","1ヶ月目","1ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,0),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="15">
         <f>IF($D$3="","2ヶ月目","2ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,1),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <f>IF($D$3="","3ヶ月目","3ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,2),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="15">
         <f>IF($D$3="","4ヶ月目","4ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,3),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="15">
         <f>IF($D$3="","5ヶ月目","5ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,4),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="15">
         <f>IF($D$3="","6ヶ月目","6ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,5),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="15">
         <f>IF($D$3="","7ヶ月目","7ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,6),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="15">
         <f>IF($D$3="","8ヶ月目","8ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,7),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="L6" s="13">
+      <c r="L6" s="15">
         <f>IF($D$3="","9ヶ月目","9ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,8),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="15">
         <f>IF($D$3="","10ヶ月目","10ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,9),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="15">
         <f>IF($D$3="","11ヶ月目","11ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,10),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="15">
         <f>IF($D$3="","12ヶ月目","12ヶ月目"&amp;CHAR(10)&amp;IFERROR(TEXT(EDATE($D$3,11),"yyyy年m月"),""))</f>
         <v/>
       </c>
-      <c r="P6" s="13" t="inlineStr">
+      <c r="P6" s="15" t="inlineStr">
         <is>
           <t>年間賞与
 (課税分)</t>
         </is>
       </c>
-      <c r="Q6" s="13" t="inlineStr">
+      <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>年間通勤手当
 (非課税分)</t>
         </is>
       </c>
-      <c r="R6" s="13" t="inlineStr">
+      <c r="R6" s="15" t="inlineStr">
         <is>
           <t>年間労働時間
 (パート必須)</t>
         </is>
       </c>
-      <c r="S6" s="13" t="inlineStr">
+      <c r="S6" s="15" t="inlineStr">
         <is>
           <t>判定
 (自動)</t>
         </is>
       </c>
-      <c r="T6" s="13" t="inlineStr">
+      <c r="T6" s="15" t="inlineStr">
         <is>
           <t>課税支給年額
 (自動)</t>
         </is>
       </c>
-      <c r="U6" s="13" t="inlineStr">
+      <c r="U6" s="15" t="inlineStr">
         <is>
           <t>FTE
 (自動)</t>
         </is>
       </c>
-      <c r="V6" s="13" t="inlineStr">
+      <c r="V6" s="15" t="inlineStr">
         <is>
           <t>警告
 (自動)</t>
@@ -1201,1170 +1217,1170 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="n"/>
-      <c r="I7" s="17" t="n"/>
-      <c r="J7" s="17" t="n"/>
-      <c r="K7" s="17" t="n"/>
-      <c r="L7" s="17" t="n"/>
-      <c r="M7" s="17" t="n"/>
-      <c r="N7" s="17" t="n"/>
-      <c r="O7" s="17" t="n"/>
-      <c r="P7" s="17" t="n"/>
-      <c r="Q7" s="17" t="n"/>
-      <c r="R7" s="17" t="n"/>
-      <c r="S7" s="18">
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="19" t="n"/>
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="19" t="n"/>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="19" t="n"/>
+      <c r="L7" s="19" t="n"/>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="19" t="n"/>
+      <c r="O7" s="19" t="n"/>
+      <c r="P7" s="19" t="n"/>
+      <c r="Q7" s="19" t="n"/>
+      <c r="R7" s="19" t="n"/>
+      <c r="S7" s="20">
         <f>IF(B7="","",IF(C7="役員","対象外（役員）",IF(NOT(OR(C7="正社員",C7="契約社員",C7="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D7:O7)=12,COUNTIF(D7:O7,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C7="パート・アルバイト",N(R7)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D7:O7)-N(Q7)+N(P7)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T7" s="19">
+      <c r="T7" s="21">
         <f>IF(S7="集計対象",SUM(D7:O7)-N(Q7)+N(P7),"")</f>
         <v/>
       </c>
-      <c r="U7" s="20">
-        <f>IF(S7&lt;&gt;"集計対象",0,IF(OR(C7="正社員",C7="契約社員"),1,N(R7)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V7" s="21">
-        <f>IF(S7="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S7="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S7="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S7="集計対象",C7="パート・アルバイト",N(R7)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U7" s="22">
+        <f>IF(S7&lt;&gt;"集計対象",0,IF(OR(C7="正社員",C7="契約社員"),1,N(R7)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V7" s="23">
+        <f>IF(S7="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S7="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S7="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S7="集計対象",C7="パート・アルバイト",N(R7)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="n"/>
-      <c r="I8" s="17" t="n"/>
-      <c r="J8" s="17" t="n"/>
-      <c r="K8" s="17" t="n"/>
-      <c r="L8" s="17" t="n"/>
-      <c r="M8" s="17" t="n"/>
-      <c r="N8" s="17" t="n"/>
-      <c r="O8" s="17" t="n"/>
-      <c r="P8" s="17" t="n"/>
-      <c r="Q8" s="17" t="n"/>
-      <c r="R8" s="17" t="n"/>
-      <c r="S8" s="18">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="19" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="19" t="n"/>
+      <c r="M8" s="19" t="n"/>
+      <c r="N8" s="19" t="n"/>
+      <c r="O8" s="19" t="n"/>
+      <c r="P8" s="19" t="n"/>
+      <c r="Q8" s="19" t="n"/>
+      <c r="R8" s="19" t="n"/>
+      <c r="S8" s="20">
         <f>IF(B8="","",IF(C8="役員","対象外（役員）",IF(NOT(OR(C8="正社員",C8="契約社員",C8="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D8:O8)=12,COUNTIF(D8:O8,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C8="パート・アルバイト",N(R8)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D8:O8)-N(Q8)+N(P8)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T8" s="19">
+      <c r="T8" s="21">
         <f>IF(S8="集計対象",SUM(D8:O8)-N(Q8)+N(P8),"")</f>
         <v/>
       </c>
-      <c r="U8" s="20">
-        <f>IF(S8&lt;&gt;"集計対象",0,IF(OR(C8="正社員",C8="契約社員"),1,N(R8)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V8" s="21">
-        <f>IF(S8="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S8="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S8="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S8="集計対象",C8="パート・アルバイト",N(R8)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U8" s="22">
+        <f>IF(S8&lt;&gt;"集計対象",0,IF(OR(C8="正社員",C8="契約社員"),1,N(R8)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V8" s="23">
+        <f>IF(S8="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S8="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S8="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S8="集計対象",C8="パート・アルバイト",N(R8)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="17" t="n"/>
-      <c r="G9" s="17" t="n"/>
-      <c r="H9" s="17" t="n"/>
-      <c r="I9" s="17" t="n"/>
-      <c r="J9" s="17" t="n"/>
-      <c r="K9" s="17" t="n"/>
-      <c r="L9" s="17" t="n"/>
-      <c r="M9" s="17" t="n"/>
-      <c r="N9" s="17" t="n"/>
-      <c r="O9" s="17" t="n"/>
-      <c r="P9" s="17" t="n"/>
-      <c r="Q9" s="17" t="n"/>
-      <c r="R9" s="17" t="n"/>
-      <c r="S9" s="18">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="19" t="n"/>
+      <c r="M9" s="19" t="n"/>
+      <c r="N9" s="19" t="n"/>
+      <c r="O9" s="19" t="n"/>
+      <c r="P9" s="19" t="n"/>
+      <c r="Q9" s="19" t="n"/>
+      <c r="R9" s="19" t="n"/>
+      <c r="S9" s="20">
         <f>IF(B9="","",IF(C9="役員","対象外（役員）",IF(NOT(OR(C9="正社員",C9="契約社員",C9="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D9:O9)=12,COUNTIF(D9:O9,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C9="パート・アルバイト",N(R9)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D9:O9)-N(Q9)+N(P9)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T9" s="19">
+      <c r="T9" s="21">
         <f>IF(S9="集計対象",SUM(D9:O9)-N(Q9)+N(P9),"")</f>
         <v/>
       </c>
-      <c r="U9" s="20">
-        <f>IF(S9&lt;&gt;"集計対象",0,IF(OR(C9="正社員",C9="契約社員"),1,N(R9)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V9" s="21">
-        <f>IF(S9="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S9="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S9="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S9="集計対象",C9="パート・アルバイト",N(R9)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U9" s="22">
+        <f>IF(S9&lt;&gt;"集計対象",0,IF(OR(C9="正社員",C9="契約社員"),1,N(R9)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V9" s="23">
+        <f>IF(S9="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S9="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S9="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S9="集計対象",C9="パート・アルバイト",N(R9)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="17" t="n"/>
-      <c r="G10" s="17" t="n"/>
-      <c r="H10" s="17" t="n"/>
-      <c r="I10" s="17" t="n"/>
-      <c r="J10" s="17" t="n"/>
-      <c r="K10" s="17" t="n"/>
-      <c r="L10" s="17" t="n"/>
-      <c r="M10" s="17" t="n"/>
-      <c r="N10" s="17" t="n"/>
-      <c r="O10" s="17" t="n"/>
-      <c r="P10" s="17" t="n"/>
-      <c r="Q10" s="17" t="n"/>
-      <c r="R10" s="17" t="n"/>
-      <c r="S10" s="18">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="19" t="n"/>
+      <c r="M10" s="19" t="n"/>
+      <c r="N10" s="19" t="n"/>
+      <c r="O10" s="19" t="n"/>
+      <c r="P10" s="19" t="n"/>
+      <c r="Q10" s="19" t="n"/>
+      <c r="R10" s="19" t="n"/>
+      <c r="S10" s="20">
         <f>IF(B10="","",IF(C10="役員","対象外（役員）",IF(NOT(OR(C10="正社員",C10="契約社員",C10="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D10:O10)=12,COUNTIF(D10:O10,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C10="パート・アルバイト",N(R10)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D10:O10)-N(Q10)+N(P10)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T10" s="19">
+      <c r="T10" s="21">
         <f>IF(S10="集計対象",SUM(D10:O10)-N(Q10)+N(P10),"")</f>
         <v/>
       </c>
-      <c r="U10" s="20">
-        <f>IF(S10&lt;&gt;"集計対象",0,IF(OR(C10="正社員",C10="契約社員"),1,N(R10)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V10" s="21">
-        <f>IF(S10="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S10="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S10="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S10="集計対象",C10="パート・アルバイト",N(R10)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U10" s="22">
+        <f>IF(S10&lt;&gt;"集計対象",0,IF(OR(C10="正社員",C10="契約社員"),1,N(R10)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V10" s="23">
+        <f>IF(S10="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S10="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S10="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S10="集計対象",C10="パート・アルバイト",N(R10)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="17" t="n"/>
-      <c r="G11" s="17" t="n"/>
-      <c r="H11" s="17" t="n"/>
-      <c r="I11" s="17" t="n"/>
-      <c r="J11" s="17" t="n"/>
-      <c r="K11" s="17" t="n"/>
-      <c r="L11" s="17" t="n"/>
-      <c r="M11" s="17" t="n"/>
-      <c r="N11" s="17" t="n"/>
-      <c r="O11" s="17" t="n"/>
-      <c r="P11" s="17" t="n"/>
-      <c r="Q11" s="17" t="n"/>
-      <c r="R11" s="17" t="n"/>
-      <c r="S11" s="18">
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="19" t="n"/>
+      <c r="M11" s="19" t="n"/>
+      <c r="N11" s="19" t="n"/>
+      <c r="O11" s="19" t="n"/>
+      <c r="P11" s="19" t="n"/>
+      <c r="Q11" s="19" t="n"/>
+      <c r="R11" s="19" t="n"/>
+      <c r="S11" s="20">
         <f>IF(B11="","",IF(C11="役員","対象外（役員）",IF(NOT(OR(C11="正社員",C11="契約社員",C11="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D11:O11)=12,COUNTIF(D11:O11,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C11="パート・アルバイト",N(R11)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D11:O11)-N(Q11)+N(P11)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T11" s="19">
+      <c r="T11" s="21">
         <f>IF(S11="集計対象",SUM(D11:O11)-N(Q11)+N(P11),"")</f>
         <v/>
       </c>
-      <c r="U11" s="20">
-        <f>IF(S11&lt;&gt;"集計対象",0,IF(OR(C11="正社員",C11="契約社員"),1,N(R11)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V11" s="21">
-        <f>IF(S11="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S11="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S11="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S11="集計対象",C11="パート・アルバイト",N(R11)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U11" s="22">
+        <f>IF(S11&lt;&gt;"集計対象",0,IF(OR(C11="正社員",C11="契約社員"),1,N(R11)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V11" s="23">
+        <f>IF(S11="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S11="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S11="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S11="集計対象",C11="パート・アルバイト",N(R11)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-      <c r="G12" s="17" t="n"/>
-      <c r="H12" s="17" t="n"/>
-      <c r="I12" s="17" t="n"/>
-      <c r="J12" s="17" t="n"/>
-      <c r="K12" s="17" t="n"/>
-      <c r="L12" s="17" t="n"/>
-      <c r="M12" s="17" t="n"/>
-      <c r="N12" s="17" t="n"/>
-      <c r="O12" s="17" t="n"/>
-      <c r="P12" s="17" t="n"/>
-      <c r="Q12" s="17" t="n"/>
-      <c r="R12" s="17" t="n"/>
-      <c r="S12" s="18">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="19" t="n"/>
+      <c r="M12" s="19" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
+      <c r="P12" s="19" t="n"/>
+      <c r="Q12" s="19" t="n"/>
+      <c r="R12" s="19" t="n"/>
+      <c r="S12" s="20">
         <f>IF(B12="","",IF(C12="役員","対象外（役員）",IF(NOT(OR(C12="正社員",C12="契約社員",C12="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D12:O12)=12,COUNTIF(D12:O12,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C12="パート・アルバイト",N(R12)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D12:O12)-N(Q12)+N(P12)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T12" s="19">
+      <c r="T12" s="21">
         <f>IF(S12="集計対象",SUM(D12:O12)-N(Q12)+N(P12),"")</f>
         <v/>
       </c>
-      <c r="U12" s="20">
-        <f>IF(S12&lt;&gt;"集計対象",0,IF(OR(C12="正社員",C12="契約社員"),1,N(R12)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V12" s="21">
-        <f>IF(S12="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S12="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S12="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S12="集計対象",C12="パート・アルバイト",N(R12)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U12" s="22">
+        <f>IF(S12&lt;&gt;"集計対象",0,IF(OR(C12="正社員",C12="契約社員"),1,N(R12)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V12" s="23">
+        <f>IF(S12="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S12="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S12="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S12="集計対象",C12="パート・アルバイト",N(R12)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="17" t="n"/>
-      <c r="G13" s="17" t="n"/>
-      <c r="H13" s="17" t="n"/>
-      <c r="I13" s="17" t="n"/>
-      <c r="J13" s="17" t="n"/>
-      <c r="K13" s="17" t="n"/>
-      <c r="L13" s="17" t="n"/>
-      <c r="M13" s="17" t="n"/>
-      <c r="N13" s="17" t="n"/>
-      <c r="O13" s="17" t="n"/>
-      <c r="P13" s="17" t="n"/>
-      <c r="Q13" s="17" t="n"/>
-      <c r="R13" s="17" t="n"/>
-      <c r="S13" s="18">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="19" t="n"/>
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="19" t="n"/>
+      <c r="O13" s="19" t="n"/>
+      <c r="P13" s="19" t="n"/>
+      <c r="Q13" s="19" t="n"/>
+      <c r="R13" s="19" t="n"/>
+      <c r="S13" s="20">
         <f>IF(B13="","",IF(C13="役員","対象外（役員）",IF(NOT(OR(C13="正社員",C13="契約社員",C13="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D13:O13)=12,COUNTIF(D13:O13,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C13="パート・アルバイト",N(R13)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D13:O13)-N(Q13)+N(P13)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T13" s="19">
+      <c r="T13" s="21">
         <f>IF(S13="集計対象",SUM(D13:O13)-N(Q13)+N(P13),"")</f>
         <v/>
       </c>
-      <c r="U13" s="20">
-        <f>IF(S13&lt;&gt;"集計対象",0,IF(OR(C13="正社員",C13="契約社員"),1,N(R13)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V13" s="21">
-        <f>IF(S13="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S13="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S13="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S13="集計対象",C13="パート・アルバイト",N(R13)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U13" s="22">
+        <f>IF(S13&lt;&gt;"集計対象",0,IF(OR(C13="正社員",C13="契約社員"),1,N(R13)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V13" s="23">
+        <f>IF(S13="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S13="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S13="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S13="集計対象",C13="パート・アルバイト",N(R13)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="17" t="n"/>
-      <c r="J14" s="17" t="n"/>
-      <c r="K14" s="17" t="n"/>
-      <c r="L14" s="17" t="n"/>
-      <c r="M14" s="17" t="n"/>
-      <c r="N14" s="17" t="n"/>
-      <c r="O14" s="17" t="n"/>
-      <c r="P14" s="17" t="n"/>
-      <c r="Q14" s="17" t="n"/>
-      <c r="R14" s="17" t="n"/>
-      <c r="S14" s="18">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="19" t="n"/>
+      <c r="M14" s="19" t="n"/>
+      <c r="N14" s="19" t="n"/>
+      <c r="O14" s="19" t="n"/>
+      <c r="P14" s="19" t="n"/>
+      <c r="Q14" s="19" t="n"/>
+      <c r="R14" s="19" t="n"/>
+      <c r="S14" s="20">
         <f>IF(B14="","",IF(C14="役員","対象外（役員）",IF(NOT(OR(C14="正社員",C14="契約社員",C14="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D14:O14)=12,COUNTIF(D14:O14,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C14="パート・アルバイト",N(R14)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D14:O14)-N(Q14)+N(P14)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T14" s="19">
+      <c r="T14" s="21">
         <f>IF(S14="集計対象",SUM(D14:O14)-N(Q14)+N(P14),"")</f>
         <v/>
       </c>
-      <c r="U14" s="20">
-        <f>IF(S14&lt;&gt;"集計対象",0,IF(OR(C14="正社員",C14="契約社員"),1,N(R14)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V14" s="21">
-        <f>IF(S14="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S14="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S14="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S14="集計対象",C14="パート・アルバイト",N(R14)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U14" s="22">
+        <f>IF(S14&lt;&gt;"集計対象",0,IF(OR(C14="正社員",C14="契約社員"),1,N(R14)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V14" s="23">
+        <f>IF(S14="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S14="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S14="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S14="集計対象",C14="パート・アルバイト",N(R14)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="17" t="n"/>
-      <c r="I15" s="17" t="n"/>
-      <c r="J15" s="17" t="n"/>
-      <c r="K15" s="17" t="n"/>
-      <c r="L15" s="17" t="n"/>
-      <c r="M15" s="17" t="n"/>
-      <c r="N15" s="17" t="n"/>
-      <c r="O15" s="17" t="n"/>
-      <c r="P15" s="17" t="n"/>
-      <c r="Q15" s="17" t="n"/>
-      <c r="R15" s="17" t="n"/>
-      <c r="S15" s="18">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="19" t="n"/>
+      <c r="M15" s="19" t="n"/>
+      <c r="N15" s="19" t="n"/>
+      <c r="O15" s="19" t="n"/>
+      <c r="P15" s="19" t="n"/>
+      <c r="Q15" s="19" t="n"/>
+      <c r="R15" s="19" t="n"/>
+      <c r="S15" s="20">
         <f>IF(B15="","",IF(C15="役員","対象外（役員）",IF(NOT(OR(C15="正社員",C15="契約社員",C15="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D15:O15)=12,COUNTIF(D15:O15,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C15="パート・アルバイト",N(R15)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D15:O15)-N(Q15)+N(P15)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T15" s="19">
+      <c r="T15" s="21">
         <f>IF(S15="集計対象",SUM(D15:O15)-N(Q15)+N(P15),"")</f>
         <v/>
       </c>
-      <c r="U15" s="20">
-        <f>IF(S15&lt;&gt;"集計対象",0,IF(OR(C15="正社員",C15="契約社員"),1,N(R15)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V15" s="21">
-        <f>IF(S15="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S15="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S15="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S15="集計対象",C15="パート・アルバイト",N(R15)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U15" s="22">
+        <f>IF(S15&lt;&gt;"集計対象",0,IF(OR(C15="正社員",C15="契約社員"),1,N(R15)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V15" s="23">
+        <f>IF(S15="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S15="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S15="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S15="集計対象",C15="パート・アルバイト",N(R15)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="17" t="n"/>
-      <c r="I16" s="17" t="n"/>
-      <c r="J16" s="17" t="n"/>
-      <c r="K16" s="17" t="n"/>
-      <c r="L16" s="17" t="n"/>
-      <c r="M16" s="17" t="n"/>
-      <c r="N16" s="17" t="n"/>
-      <c r="O16" s="17" t="n"/>
-      <c r="P16" s="17" t="n"/>
-      <c r="Q16" s="17" t="n"/>
-      <c r="R16" s="17" t="n"/>
-      <c r="S16" s="18">
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="19" t="n"/>
+      <c r="M16" s="19" t="n"/>
+      <c r="N16" s="19" t="n"/>
+      <c r="O16" s="19" t="n"/>
+      <c r="P16" s="19" t="n"/>
+      <c r="Q16" s="19" t="n"/>
+      <c r="R16" s="19" t="n"/>
+      <c r="S16" s="20">
         <f>IF(B16="","",IF(C16="役員","対象外（役員）",IF(NOT(OR(C16="正社員",C16="契約社員",C16="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D16:O16)=12,COUNTIF(D16:O16,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C16="パート・アルバイト",N(R16)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D16:O16)-N(Q16)+N(P16)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T16" s="19">
+      <c r="T16" s="21">
         <f>IF(S16="集計対象",SUM(D16:O16)-N(Q16)+N(P16),"")</f>
         <v/>
       </c>
-      <c r="U16" s="20">
-        <f>IF(S16&lt;&gt;"集計対象",0,IF(OR(C16="正社員",C16="契約社員"),1,N(R16)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V16" s="21">
-        <f>IF(S16="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S16="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S16="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S16="集計対象",C16="パート・アルバイト",N(R16)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U16" s="22">
+        <f>IF(S16&lt;&gt;"集計対象",0,IF(OR(C16="正社員",C16="契約社員"),1,N(R16)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V16" s="23">
+        <f>IF(S16="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S16="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S16="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S16="集計対象",C16="パート・アルバイト",N(R16)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="n">
+      <c r="A17" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="17" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="17" t="n"/>
-      <c r="I17" s="17" t="n"/>
-      <c r="J17" s="17" t="n"/>
-      <c r="K17" s="17" t="n"/>
-      <c r="L17" s="17" t="n"/>
-      <c r="M17" s="17" t="n"/>
-      <c r="N17" s="17" t="n"/>
-      <c r="O17" s="17" t="n"/>
-      <c r="P17" s="17" t="n"/>
-      <c r="Q17" s="17" t="n"/>
-      <c r="R17" s="17" t="n"/>
-      <c r="S17" s="18">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="19" t="n"/>
+      <c r="M17" s="19" t="n"/>
+      <c r="N17" s="19" t="n"/>
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="19" t="n"/>
+      <c r="Q17" s="19" t="n"/>
+      <c r="R17" s="19" t="n"/>
+      <c r="S17" s="20">
         <f>IF(B17="","",IF(C17="役員","対象外（役員）",IF(NOT(OR(C17="正社員",C17="契約社員",C17="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D17:O17)=12,COUNTIF(D17:O17,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C17="パート・アルバイト",N(R17)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D17:O17)-N(Q17)+N(P17)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T17" s="19">
+      <c r="T17" s="21">
         <f>IF(S17="集計対象",SUM(D17:O17)-N(Q17)+N(P17),"")</f>
         <v/>
       </c>
-      <c r="U17" s="20">
-        <f>IF(S17&lt;&gt;"集計対象",0,IF(OR(C17="正社員",C17="契約社員"),1,N(R17)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V17" s="21">
-        <f>IF(S17="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S17="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S17="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S17="集計対象",C17="パート・アルバイト",N(R17)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U17" s="22">
+        <f>IF(S17&lt;&gt;"集計対象",0,IF(OR(C17="正社員",C17="契約社員"),1,N(R17)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V17" s="23">
+        <f>IF(S17="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S17="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S17="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S17="集計対象",C17="パート・アルバイト",N(R17)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="n">
+      <c r="A18" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="n"/>
-      <c r="I18" s="17" t="n"/>
-      <c r="J18" s="17" t="n"/>
-      <c r="K18" s="17" t="n"/>
-      <c r="L18" s="17" t="n"/>
-      <c r="M18" s="17" t="n"/>
-      <c r="N18" s="17" t="n"/>
-      <c r="O18" s="17" t="n"/>
-      <c r="P18" s="17" t="n"/>
-      <c r="Q18" s="17" t="n"/>
-      <c r="R18" s="17" t="n"/>
-      <c r="S18" s="18">
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="19" t="n"/>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="19" t="n"/>
+      <c r="Q18" s="19" t="n"/>
+      <c r="R18" s="19" t="n"/>
+      <c r="S18" s="20">
         <f>IF(B18="","",IF(C18="役員","対象外（役員）",IF(NOT(OR(C18="正社員",C18="契約社員",C18="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D18:O18)=12,COUNTIF(D18:O18,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C18="パート・アルバイト",N(R18)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D18:O18)-N(Q18)+N(P18)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T18" s="19">
+      <c r="T18" s="21">
         <f>IF(S18="集計対象",SUM(D18:O18)-N(Q18)+N(P18),"")</f>
         <v/>
       </c>
-      <c r="U18" s="20">
-        <f>IF(S18&lt;&gt;"集計対象",0,IF(OR(C18="正社員",C18="契約社員"),1,N(R18)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V18" s="21">
-        <f>IF(S18="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S18="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S18="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S18="集計対象",C18="パート・アルバイト",N(R18)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U18" s="22">
+        <f>IF(S18&lt;&gt;"集計対象",0,IF(OR(C18="正社員",C18="契約社員"),1,N(R18)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V18" s="23">
+        <f>IF(S18="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S18="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S18="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S18="集計対象",C18="パート・アルバイト",N(R18)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="n">
+      <c r="A19" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="17" t="n"/>
-      <c r="I19" s="17" t="n"/>
-      <c r="J19" s="17" t="n"/>
-      <c r="K19" s="17" t="n"/>
-      <c r="L19" s="17" t="n"/>
-      <c r="M19" s="17" t="n"/>
-      <c r="N19" s="17" t="n"/>
-      <c r="O19" s="17" t="n"/>
-      <c r="P19" s="17" t="n"/>
-      <c r="Q19" s="17" t="n"/>
-      <c r="R19" s="17" t="n"/>
-      <c r="S19" s="18">
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="19" t="n"/>
+      <c r="M19" s="19" t="n"/>
+      <c r="N19" s="19" t="n"/>
+      <c r="O19" s="19" t="n"/>
+      <c r="P19" s="19" t="n"/>
+      <c r="Q19" s="19" t="n"/>
+      <c r="R19" s="19" t="n"/>
+      <c r="S19" s="20">
         <f>IF(B19="","",IF(C19="役員","対象外（役員）",IF(NOT(OR(C19="正社員",C19="契約社員",C19="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D19:O19)=12,COUNTIF(D19:O19,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C19="パート・アルバイト",N(R19)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D19:O19)-N(Q19)+N(P19)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T19" s="19">
+      <c r="T19" s="21">
         <f>IF(S19="集計対象",SUM(D19:O19)-N(Q19)+N(P19),"")</f>
         <v/>
       </c>
-      <c r="U19" s="20">
-        <f>IF(S19&lt;&gt;"集計対象",0,IF(OR(C19="正社員",C19="契約社員"),1,N(R19)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V19" s="21">
-        <f>IF(S19="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S19="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S19="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S19="集計対象",C19="パート・アルバイト",N(R19)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U19" s="22">
+        <f>IF(S19&lt;&gt;"集計対象",0,IF(OR(C19="正社員",C19="契約社員"),1,N(R19)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V19" s="23">
+        <f>IF(S19="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S19="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S19="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S19="集計対象",C19="パート・アルバイト",N(R19)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="n">
+      <c r="A20" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="17" t="n"/>
-      <c r="H20" s="17" t="n"/>
-      <c r="I20" s="17" t="n"/>
-      <c r="J20" s="17" t="n"/>
-      <c r="K20" s="17" t="n"/>
-      <c r="L20" s="17" t="n"/>
-      <c r="M20" s="17" t="n"/>
-      <c r="N20" s="17" t="n"/>
-      <c r="O20" s="17" t="n"/>
-      <c r="P20" s="17" t="n"/>
-      <c r="Q20" s="17" t="n"/>
-      <c r="R20" s="17" t="n"/>
-      <c r="S20" s="18">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="19" t="n"/>
+      <c r="M20" s="19" t="n"/>
+      <c r="N20" s="19" t="n"/>
+      <c r="O20" s="19" t="n"/>
+      <c r="P20" s="19" t="n"/>
+      <c r="Q20" s="19" t="n"/>
+      <c r="R20" s="19" t="n"/>
+      <c r="S20" s="20">
         <f>IF(B20="","",IF(C20="役員","対象外（役員）",IF(NOT(OR(C20="正社員",C20="契約社員",C20="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D20:O20)=12,COUNTIF(D20:O20,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C20="パート・アルバイト",N(R20)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D20:O20)-N(Q20)+N(P20)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T20" s="19">
+      <c r="T20" s="21">
         <f>IF(S20="集計対象",SUM(D20:O20)-N(Q20)+N(P20),"")</f>
         <v/>
       </c>
-      <c r="U20" s="20">
-        <f>IF(S20&lt;&gt;"集計対象",0,IF(OR(C20="正社員",C20="契約社員"),1,N(R20)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V20" s="21">
-        <f>IF(S20="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S20="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S20="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S20="集計対象",C20="パート・アルバイト",N(R20)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U20" s="22">
+        <f>IF(S20&lt;&gt;"集計対象",0,IF(OR(C20="正社員",C20="契約社員"),1,N(R20)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V20" s="23">
+        <f>IF(S20="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S20="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S20="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S20="集計対象",C20="パート・アルバイト",N(R20)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="n">
+      <c r="A21" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="17" t="n"/>
-      <c r="J21" s="17" t="n"/>
-      <c r="K21" s="17" t="n"/>
-      <c r="L21" s="17" t="n"/>
-      <c r="M21" s="17" t="n"/>
-      <c r="N21" s="17" t="n"/>
-      <c r="O21" s="17" t="n"/>
-      <c r="P21" s="17" t="n"/>
-      <c r="Q21" s="17" t="n"/>
-      <c r="R21" s="17" t="n"/>
-      <c r="S21" s="18">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="19" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="19" t="n"/>
+      <c r="Q21" s="19" t="n"/>
+      <c r="R21" s="19" t="n"/>
+      <c r="S21" s="20">
         <f>IF(B21="","",IF(C21="役員","対象外（役員）",IF(NOT(OR(C21="正社員",C21="契約社員",C21="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D21:O21)=12,COUNTIF(D21:O21,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C21="パート・アルバイト",N(R21)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D21:O21)-N(Q21)+N(P21)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T21" s="19">
+      <c r="T21" s="21">
         <f>IF(S21="集計対象",SUM(D21:O21)-N(Q21)+N(P21),"")</f>
         <v/>
       </c>
-      <c r="U21" s="20">
-        <f>IF(S21&lt;&gt;"集計対象",0,IF(OR(C21="正社員",C21="契約社員"),1,N(R21)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V21" s="21">
-        <f>IF(S21="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S21="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S21="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S21="集計対象",C21="パート・アルバイト",N(R21)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U21" s="22">
+        <f>IF(S21&lt;&gt;"集計対象",0,IF(OR(C21="正社員",C21="契約社員"),1,N(R21)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V21" s="23">
+        <f>IF(S21="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S21="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S21="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S21="集計対象",C21="パート・アルバイト",N(R21)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="n">
+      <c r="A22" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-      <c r="I22" s="17" t="n"/>
-      <c r="J22" s="17" t="n"/>
-      <c r="K22" s="17" t="n"/>
-      <c r="L22" s="17" t="n"/>
-      <c r="M22" s="17" t="n"/>
-      <c r="N22" s="17" t="n"/>
-      <c r="O22" s="17" t="n"/>
-      <c r="P22" s="17" t="n"/>
-      <c r="Q22" s="17" t="n"/>
-      <c r="R22" s="17" t="n"/>
-      <c r="S22" s="18">
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="19" t="n"/>
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="n"/>
+      <c r="O22" s="19" t="n"/>
+      <c r="P22" s="19" t="n"/>
+      <c r="Q22" s="19" t="n"/>
+      <c r="R22" s="19" t="n"/>
+      <c r="S22" s="20">
         <f>IF(B22="","",IF(C22="役員","対象外（役員）",IF(NOT(OR(C22="正社員",C22="契約社員",C22="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D22:O22)=12,COUNTIF(D22:O22,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C22="パート・アルバイト",N(R22)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D22:O22)-N(Q22)+N(P22)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T22" s="19">
+      <c r="T22" s="21">
         <f>IF(S22="集計対象",SUM(D22:O22)-N(Q22)+N(P22),"")</f>
         <v/>
       </c>
-      <c r="U22" s="20">
-        <f>IF(S22&lt;&gt;"集計対象",0,IF(OR(C22="正社員",C22="契約社員"),1,N(R22)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V22" s="21">
-        <f>IF(S22="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S22="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S22="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S22="集計対象",C22="パート・アルバイト",N(R22)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U22" s="22">
+        <f>IF(S22&lt;&gt;"集計対象",0,IF(OR(C22="正社員",C22="契約社員"),1,N(R22)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V22" s="23">
+        <f>IF(S22="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S22="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S22="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S22="集計対象",C22="パート・アルバイト",N(R22)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="n">
+      <c r="A23" s="16" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="17" t="n"/>
-      <c r="G23" s="17" t="n"/>
-      <c r="H23" s="17" t="n"/>
-      <c r="I23" s="17" t="n"/>
-      <c r="J23" s="17" t="n"/>
-      <c r="K23" s="17" t="n"/>
-      <c r="L23" s="17" t="n"/>
-      <c r="M23" s="17" t="n"/>
-      <c r="N23" s="17" t="n"/>
-      <c r="O23" s="17" t="n"/>
-      <c r="P23" s="17" t="n"/>
-      <c r="Q23" s="17" t="n"/>
-      <c r="R23" s="17" t="n"/>
-      <c r="S23" s="18">
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="19" t="n"/>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="19" t="n"/>
+      <c r="Q23" s="19" t="n"/>
+      <c r="R23" s="19" t="n"/>
+      <c r="S23" s="20">
         <f>IF(B23="","",IF(C23="役員","対象外（役員）",IF(NOT(OR(C23="正社員",C23="契約社員",C23="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D23:O23)=12,COUNTIF(D23:O23,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C23="パート・アルバイト",N(R23)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D23:O23)-N(Q23)+N(P23)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T23" s="19">
+      <c r="T23" s="21">
         <f>IF(S23="集計対象",SUM(D23:O23)-N(Q23)+N(P23),"")</f>
         <v/>
       </c>
-      <c r="U23" s="20">
-        <f>IF(S23&lt;&gt;"集計対象",0,IF(OR(C23="正社員",C23="契約社員"),1,N(R23)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V23" s="21">
-        <f>IF(S23="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S23="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S23="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S23="集計対象",C23="パート・アルバイト",N(R23)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U23" s="22">
+        <f>IF(S23&lt;&gt;"集計対象",0,IF(OR(C23="正社員",C23="契約社員"),1,N(R23)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V23" s="23">
+        <f>IF(S23="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S23="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S23="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S23="集計対象",C23="パート・アルバイト",N(R23)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="n">
+      <c r="A24" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
-      <c r="H24" s="17" t="n"/>
-      <c r="I24" s="17" t="n"/>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="17" t="n"/>
-      <c r="L24" s="17" t="n"/>
-      <c r="M24" s="17" t="n"/>
-      <c r="N24" s="17" t="n"/>
-      <c r="O24" s="17" t="n"/>
-      <c r="P24" s="17" t="n"/>
-      <c r="Q24" s="17" t="n"/>
-      <c r="R24" s="17" t="n"/>
-      <c r="S24" s="18">
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="19" t="n"/>
+      <c r="I24" s="19" t="n"/>
+      <c r="J24" s="19" t="n"/>
+      <c r="K24" s="19" t="n"/>
+      <c r="L24" s="19" t="n"/>
+      <c r="M24" s="19" t="n"/>
+      <c r="N24" s="19" t="n"/>
+      <c r="O24" s="19" t="n"/>
+      <c r="P24" s="19" t="n"/>
+      <c r="Q24" s="19" t="n"/>
+      <c r="R24" s="19" t="n"/>
+      <c r="S24" s="20">
         <f>IF(B24="","",IF(C24="役員","対象外（役員）",IF(NOT(OR(C24="正社員",C24="契約社員",C24="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D24:O24)=12,COUNTIF(D24:O24,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C24="パート・アルバイト",N(R24)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D24:O24)-N(Q24)+N(P24)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T24" s="19">
+      <c r="T24" s="21">
         <f>IF(S24="集計対象",SUM(D24:O24)-N(Q24)+N(P24),"")</f>
         <v/>
       </c>
-      <c r="U24" s="20">
-        <f>IF(S24&lt;&gt;"集計対象",0,IF(OR(C24="正社員",C24="契約社員"),1,N(R24)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V24" s="21">
-        <f>IF(S24="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S24="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S24="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S24="集計対象",C24="パート・アルバイト",N(R24)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U24" s="22">
+        <f>IF(S24&lt;&gt;"集計対象",0,IF(OR(C24="正社員",C24="契約社員"),1,N(R24)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V24" s="23">
+        <f>IF(S24="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S24="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S24="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S24="集計対象",C24="パート・アルバイト",N(R24)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="n">
+      <c r="A25" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="17" t="n"/>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="17" t="n"/>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="17" t="n"/>
-      <c r="L25" s="17" t="n"/>
-      <c r="M25" s="17" t="n"/>
-      <c r="N25" s="17" t="n"/>
-      <c r="O25" s="17" t="n"/>
-      <c r="P25" s="17" t="n"/>
-      <c r="Q25" s="17" t="n"/>
-      <c r="R25" s="17" t="n"/>
-      <c r="S25" s="18">
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="19" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="19" t="n"/>
+      <c r="I25" s="19" t="n"/>
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="19" t="n"/>
+      <c r="M25" s="19" t="n"/>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="19" t="n"/>
+      <c r="Q25" s="19" t="n"/>
+      <c r="R25" s="19" t="n"/>
+      <c r="S25" s="20">
         <f>IF(B25="","",IF(C25="役員","対象外（役員）",IF(NOT(OR(C25="正社員",C25="契約社員",C25="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D25:O25)=12,COUNTIF(D25:O25,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C25="パート・アルバイト",N(R25)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D25:O25)-N(Q25)+N(P25)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T25" s="19">
+      <c r="T25" s="21">
         <f>IF(S25="集計対象",SUM(D25:O25)-N(Q25)+N(P25),"")</f>
         <v/>
       </c>
-      <c r="U25" s="20">
-        <f>IF(S25&lt;&gt;"集計対象",0,IF(OR(C25="正社員",C25="契約社員"),1,N(R25)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V25" s="21">
-        <f>IF(S25="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S25="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S25="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S25="集計対象",C25="パート・アルバイト",N(R25)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U25" s="22">
+        <f>IF(S25&lt;&gt;"集計対象",0,IF(OR(C25="正社員",C25="契約社員"),1,N(R25)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V25" s="23">
+        <f>IF(S25="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S25="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S25="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S25="集計対象",C25="パート・アルバイト",N(R25)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="n">
+      <c r="A26" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="17" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="17" t="n"/>
-      <c r="L26" s="17" t="n"/>
-      <c r="M26" s="17" t="n"/>
-      <c r="N26" s="17" t="n"/>
-      <c r="O26" s="17" t="n"/>
-      <c r="P26" s="17" t="n"/>
-      <c r="Q26" s="17" t="n"/>
-      <c r="R26" s="17" t="n"/>
-      <c r="S26" s="18">
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="19" t="n"/>
+      <c r="I26" s="19" t="n"/>
+      <c r="J26" s="19" t="n"/>
+      <c r="K26" s="19" t="n"/>
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="19" t="n"/>
+      <c r="N26" s="19" t="n"/>
+      <c r="O26" s="19" t="n"/>
+      <c r="P26" s="19" t="n"/>
+      <c r="Q26" s="19" t="n"/>
+      <c r="R26" s="19" t="n"/>
+      <c r="S26" s="20">
         <f>IF(B26="","",IF(C26="役員","対象外（役員）",IF(NOT(OR(C26="正社員",C26="契約社員",C26="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D26:O26)=12,COUNTIF(D26:O26,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C26="パート・アルバイト",N(R26)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D26:O26)-N(Q26)+N(P26)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T26" s="19">
+      <c r="T26" s="21">
         <f>IF(S26="集計対象",SUM(D26:O26)-N(Q26)+N(P26),"")</f>
         <v/>
       </c>
-      <c r="U26" s="20">
-        <f>IF(S26&lt;&gt;"集計対象",0,IF(OR(C26="正社員",C26="契約社員"),1,N(R26)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V26" s="21">
-        <f>IF(S26="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S26="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S26="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S26="集計対象",C26="パート・アルバイト",N(R26)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U26" s="22">
+        <f>IF(S26&lt;&gt;"集計対象",0,IF(OR(C26="正社員",C26="契約社員"),1,N(R26)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V26" s="23">
+        <f>IF(S26="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S26="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S26="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S26="集計対象",C26="パート・アルバイト",N(R26)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="n">
+      <c r="A27" s="16" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="n"/>
-      <c r="I27" s="17" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="17" t="n"/>
-      <c r="L27" s="17" t="n"/>
-      <c r="M27" s="17" t="n"/>
-      <c r="N27" s="17" t="n"/>
-      <c r="O27" s="17" t="n"/>
-      <c r="P27" s="17" t="n"/>
-      <c r="Q27" s="17" t="n"/>
-      <c r="R27" s="17" t="n"/>
-      <c r="S27" s="18">
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="19" t="n"/>
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="19" t="n"/>
+      <c r="O27" s="19" t="n"/>
+      <c r="P27" s="19" t="n"/>
+      <c r="Q27" s="19" t="n"/>
+      <c r="R27" s="19" t="n"/>
+      <c r="S27" s="20">
         <f>IF(B27="","",IF(C27="役員","対象外（役員）",IF(NOT(OR(C27="正社員",C27="契約社員",C27="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D27:O27)=12,COUNTIF(D27:O27,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C27="パート・アルバイト",N(R27)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D27:O27)-N(Q27)+N(P27)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T27" s="19">
+      <c r="T27" s="21">
         <f>IF(S27="集計対象",SUM(D27:O27)-N(Q27)+N(P27),"")</f>
         <v/>
       </c>
-      <c r="U27" s="20">
-        <f>IF(S27&lt;&gt;"集計対象",0,IF(OR(C27="正社員",C27="契約社員"),1,N(R27)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V27" s="21">
-        <f>IF(S27="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S27="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S27="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S27="集計対象",C27="パート・アルバイト",N(R27)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U27" s="22">
+        <f>IF(S27&lt;&gt;"集計対象",0,IF(OR(C27="正社員",C27="契約社員"),1,N(R27)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V27" s="23">
+        <f>IF(S27="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S27="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S27="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S27="集計対象",C27="パート・アルバイト",N(R27)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="n">
+      <c r="A28" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="17" t="n"/>
-      <c r="H28" s="17" t="n"/>
-      <c r="I28" s="17" t="n"/>
-      <c r="J28" s="17" t="n"/>
-      <c r="K28" s="17" t="n"/>
-      <c r="L28" s="17" t="n"/>
-      <c r="M28" s="17" t="n"/>
-      <c r="N28" s="17" t="n"/>
-      <c r="O28" s="17" t="n"/>
-      <c r="P28" s="17" t="n"/>
-      <c r="Q28" s="17" t="n"/>
-      <c r="R28" s="17" t="n"/>
-      <c r="S28" s="18">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="19" t="n"/>
+      <c r="H28" s="19" t="n"/>
+      <c r="I28" s="19" t="n"/>
+      <c r="J28" s="19" t="n"/>
+      <c r="K28" s="19" t="n"/>
+      <c r="L28" s="19" t="n"/>
+      <c r="M28" s="19" t="n"/>
+      <c r="N28" s="19" t="n"/>
+      <c r="O28" s="19" t="n"/>
+      <c r="P28" s="19" t="n"/>
+      <c r="Q28" s="19" t="n"/>
+      <c r="R28" s="19" t="n"/>
+      <c r="S28" s="20">
         <f>IF(B28="","",IF(C28="役員","対象外（役員）",IF(NOT(OR(C28="正社員",C28="契約社員",C28="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D28:O28)=12,COUNTIF(D28:O28,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C28="パート・アルバイト",N(R28)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D28:O28)-N(Q28)+N(P28)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T28" s="19">
+      <c r="T28" s="21">
         <f>IF(S28="集計対象",SUM(D28:O28)-N(Q28)+N(P28),"")</f>
         <v/>
       </c>
-      <c r="U28" s="20">
-        <f>IF(S28&lt;&gt;"集計対象",0,IF(OR(C28="正社員",C28="契約社員"),1,N(R28)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V28" s="21">
-        <f>IF(S28="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S28="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S28="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S28="集計対象",C28="パート・アルバイト",N(R28)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U28" s="22">
+        <f>IF(S28&lt;&gt;"集計対象",0,IF(OR(C28="正社員",C28="契約社員"),1,N(R28)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V28" s="23">
+        <f>IF(S28="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S28="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S28="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S28="集計対象",C28="パート・アルバイト",N(R28)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="n">
+      <c r="A29" s="16" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="17" t="n"/>
-      <c r="H29" s="17" t="n"/>
-      <c r="I29" s="17" t="n"/>
-      <c r="J29" s="17" t="n"/>
-      <c r="K29" s="17" t="n"/>
-      <c r="L29" s="17" t="n"/>
-      <c r="M29" s="17" t="n"/>
-      <c r="N29" s="17" t="n"/>
-      <c r="O29" s="17" t="n"/>
-      <c r="P29" s="17" t="n"/>
-      <c r="Q29" s="17" t="n"/>
-      <c r="R29" s="17" t="n"/>
-      <c r="S29" s="18">
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+      <c r="H29" s="19" t="n"/>
+      <c r="I29" s="19" t="n"/>
+      <c r="J29" s="19" t="n"/>
+      <c r="K29" s="19" t="n"/>
+      <c r="L29" s="19" t="n"/>
+      <c r="M29" s="19" t="n"/>
+      <c r="N29" s="19" t="n"/>
+      <c r="O29" s="19" t="n"/>
+      <c r="P29" s="19" t="n"/>
+      <c r="Q29" s="19" t="n"/>
+      <c r="R29" s="19" t="n"/>
+      <c r="S29" s="20">
         <f>IF(B29="","",IF(C29="役員","対象外（役員）",IF(NOT(OR(C29="正社員",C29="契約社員",C29="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D29:O29)=12,COUNTIF(D29:O29,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C29="パート・アルバイト",N(R29)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D29:O29)-N(Q29)+N(P29)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T29" s="19">
+      <c r="T29" s="21">
         <f>IF(S29="集計対象",SUM(D29:O29)-N(Q29)+N(P29),"")</f>
         <v/>
       </c>
-      <c r="U29" s="20">
-        <f>IF(S29&lt;&gt;"集計対象",0,IF(OR(C29="正社員",C29="契約社員"),1,N(R29)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V29" s="21">
-        <f>IF(S29="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S29="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S29="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S29="集計対象",C29="パート・アルバイト",N(R29)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U29" s="22">
+        <f>IF(S29&lt;&gt;"集計対象",0,IF(OR(C29="正社員",C29="契約社員"),1,N(R29)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V29" s="23">
+        <f>IF(S29="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S29="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S29="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S29="集計対象",C29="パート・アルバイト",N(R29)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="n">
+      <c r="A30" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="17" t="n"/>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="17" t="n"/>
-      <c r="L30" s="17" t="n"/>
-      <c r="M30" s="17" t="n"/>
-      <c r="N30" s="17" t="n"/>
-      <c r="O30" s="17" t="n"/>
-      <c r="P30" s="17" t="n"/>
-      <c r="Q30" s="17" t="n"/>
-      <c r="R30" s="17" t="n"/>
-      <c r="S30" s="18">
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="19" t="n"/>
+      <c r="J30" s="19" t="n"/>
+      <c r="K30" s="19" t="n"/>
+      <c r="L30" s="19" t="n"/>
+      <c r="M30" s="19" t="n"/>
+      <c r="N30" s="19" t="n"/>
+      <c r="O30" s="19" t="n"/>
+      <c r="P30" s="19" t="n"/>
+      <c r="Q30" s="19" t="n"/>
+      <c r="R30" s="19" t="n"/>
+      <c r="S30" s="20">
         <f>IF(B30="","",IF(C30="役員","対象外（役員）",IF(NOT(OR(C30="正社員",C30="契約社員",C30="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D30:O30)=12,COUNTIF(D30:O30,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C30="パート・アルバイト",N(R30)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D30:O30)-N(Q30)+N(P30)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T30" s="19">
+      <c r="T30" s="21">
         <f>IF(S30="集計対象",SUM(D30:O30)-N(Q30)+N(P30),"")</f>
         <v/>
       </c>
-      <c r="U30" s="20">
-        <f>IF(S30&lt;&gt;"集計対象",0,IF(OR(C30="正社員",C30="契約社員"),1,N(R30)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V30" s="21">
-        <f>IF(S30="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S30="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S30="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S30="集計対象",C30="パート・アルバイト",N(R30)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U30" s="22">
+        <f>IF(S30&lt;&gt;"集計対象",0,IF(OR(C30="正社員",C30="契約社員"),1,N(R30)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V30" s="23">
+        <f>IF(S30="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S30="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S30="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S30="集計対象",C30="パート・アルバイト",N(R30)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="n">
+      <c r="A31" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="17" t="n"/>
-      <c r="G31" s="17" t="n"/>
-      <c r="H31" s="17" t="n"/>
-      <c r="I31" s="17" t="n"/>
-      <c r="J31" s="17" t="n"/>
-      <c r="K31" s="17" t="n"/>
-      <c r="L31" s="17" t="n"/>
-      <c r="M31" s="17" t="n"/>
-      <c r="N31" s="17" t="n"/>
-      <c r="O31" s="17" t="n"/>
-      <c r="P31" s="17" t="n"/>
-      <c r="Q31" s="17" t="n"/>
-      <c r="R31" s="17" t="n"/>
-      <c r="S31" s="18">
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="19" t="n"/>
+      <c r="I31" s="19" t="n"/>
+      <c r="J31" s="19" t="n"/>
+      <c r="K31" s="19" t="n"/>
+      <c r="L31" s="19" t="n"/>
+      <c r="M31" s="19" t="n"/>
+      <c r="N31" s="19" t="n"/>
+      <c r="O31" s="19" t="n"/>
+      <c r="P31" s="19" t="n"/>
+      <c r="Q31" s="19" t="n"/>
+      <c r="R31" s="19" t="n"/>
+      <c r="S31" s="20">
         <f>IF(B31="","",IF(C31="役員","対象外（役員）",IF(NOT(OR(C31="正社員",C31="契約社員",C31="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D31:O31)=12,COUNTIF(D31:O31,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C31="パート・アルバイト",N(R31)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D31:O31)-N(Q31)+N(P31)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T31" s="19">
+      <c r="T31" s="21">
         <f>IF(S31="集計対象",SUM(D31:O31)-N(Q31)+N(P31),"")</f>
         <v/>
       </c>
-      <c r="U31" s="20">
-        <f>IF(S31&lt;&gt;"集計対象",0,IF(OR(C31="正社員",C31="契約社員"),1,N(R31)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V31" s="21">
-        <f>IF(S31="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S31="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S31="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S31="集計対象",C31="パート・アルバイト",N(R31)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U31" s="22">
+        <f>IF(S31&lt;&gt;"集計対象",0,IF(OR(C31="正社員",C31="契約社員"),1,N(R31)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V31" s="23">
+        <f>IF(S31="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S31="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S31="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S31="集計対象",C31="パート・アルバイト",N(R31)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="n">
+      <c r="A32" s="16" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="15" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="17" t="n"/>
-      <c r="F32" s="17" t="n"/>
-      <c r="G32" s="17" t="n"/>
-      <c r="H32" s="17" t="n"/>
-      <c r="I32" s="17" t="n"/>
-      <c r="J32" s="17" t="n"/>
-      <c r="K32" s="17" t="n"/>
-      <c r="L32" s="17" t="n"/>
-      <c r="M32" s="17" t="n"/>
-      <c r="N32" s="17" t="n"/>
-      <c r="O32" s="17" t="n"/>
-      <c r="P32" s="17" t="n"/>
-      <c r="Q32" s="17" t="n"/>
-      <c r="R32" s="17" t="n"/>
-      <c r="S32" s="18">
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="19" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="19" t="n"/>
+      <c r="H32" s="19" t="n"/>
+      <c r="I32" s="19" t="n"/>
+      <c r="J32" s="19" t="n"/>
+      <c r="K32" s="19" t="n"/>
+      <c r="L32" s="19" t="n"/>
+      <c r="M32" s="19" t="n"/>
+      <c r="N32" s="19" t="n"/>
+      <c r="O32" s="19" t="n"/>
+      <c r="P32" s="19" t="n"/>
+      <c r="Q32" s="19" t="n"/>
+      <c r="R32" s="19" t="n"/>
+      <c r="S32" s="20">
         <f>IF(B32="","",IF(C32="役員","対象外（役員）",IF(NOT(OR(C32="正社員",C32="契約社員",C32="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D32:O32)=12,COUNTIF(D32:O32,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C32="パート・アルバイト",N(R32)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D32:O32)-N(Q32)+N(P32)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T32" s="19">
+      <c r="T32" s="21">
         <f>IF(S32="集計対象",SUM(D32:O32)-N(Q32)+N(P32),"")</f>
         <v/>
       </c>
-      <c r="U32" s="20">
-        <f>IF(S32&lt;&gt;"集計対象",0,IF(OR(C32="正社員",C32="契約社員"),1,N(R32)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V32" s="21">
-        <f>IF(S32="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S32="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S32="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S32="集計対象",C32="パート・アルバイト",N(R32)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U32" s="22">
+        <f>IF(S32&lt;&gt;"集計対象",0,IF(OR(C32="正社員",C32="契約社員"),1,N(R32)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V32" s="23">
+        <f>IF(S32="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S32="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S32="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S32="集計対象",C32="パート・アルバイト",N(R32)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="n">
+      <c r="A33" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="17" t="n"/>
-      <c r="G33" s="17" t="n"/>
-      <c r="H33" s="17" t="n"/>
-      <c r="I33" s="17" t="n"/>
-      <c r="J33" s="17" t="n"/>
-      <c r="K33" s="17" t="n"/>
-      <c r="L33" s="17" t="n"/>
-      <c r="M33" s="17" t="n"/>
-      <c r="N33" s="17" t="n"/>
-      <c r="O33" s="17" t="n"/>
-      <c r="P33" s="17" t="n"/>
-      <c r="Q33" s="17" t="n"/>
-      <c r="R33" s="17" t="n"/>
-      <c r="S33" s="18">
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19" t="n"/>
+      <c r="J33" s="19" t="n"/>
+      <c r="K33" s="19" t="n"/>
+      <c r="L33" s="19" t="n"/>
+      <c r="M33" s="19" t="n"/>
+      <c r="N33" s="19" t="n"/>
+      <c r="O33" s="19" t="n"/>
+      <c r="P33" s="19" t="n"/>
+      <c r="Q33" s="19" t="n"/>
+      <c r="R33" s="19" t="n"/>
+      <c r="S33" s="20">
         <f>IF(B33="","",IF(C33="役員","対象外（役員）",IF(NOT(OR(C33="正社員",C33="契約社員",C33="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D33:O33)=12,COUNTIF(D33:O33,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C33="パート・アルバイト",N(R33)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D33:O33)-N(Q33)+N(P33)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T33" s="19">
+      <c r="T33" s="21">
         <f>IF(S33="集計対象",SUM(D33:O33)-N(Q33)+N(P33),"")</f>
         <v/>
       </c>
-      <c r="U33" s="20">
-        <f>IF(S33&lt;&gt;"集計対象",0,IF(OR(C33="正社員",C33="契約社員"),1,N(R33)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V33" s="21">
-        <f>IF(S33="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S33="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S33="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S33="集計対象",C33="パート・アルバイト",N(R33)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U33" s="22">
+        <f>IF(S33&lt;&gt;"集計対象",0,IF(OR(C33="正社員",C33="契約社員"),1,N(R33)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V33" s="23">
+        <f>IF(S33="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S33="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S33="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S33="集計対象",C33="パート・アルバイト",N(R33)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="n">
+      <c r="A34" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="n"/>
-      <c r="F34" s="17" t="n"/>
-      <c r="G34" s="17" t="n"/>
-      <c r="H34" s="17" t="n"/>
-      <c r="I34" s="17" t="n"/>
-      <c r="J34" s="17" t="n"/>
-      <c r="K34" s="17" t="n"/>
-      <c r="L34" s="17" t="n"/>
-      <c r="M34" s="17" t="n"/>
-      <c r="N34" s="17" t="n"/>
-      <c r="O34" s="17" t="n"/>
-      <c r="P34" s="17" t="n"/>
-      <c r="Q34" s="17" t="n"/>
-      <c r="R34" s="17" t="n"/>
-      <c r="S34" s="18">
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="19" t="n"/>
+      <c r="H34" s="19" t="n"/>
+      <c r="I34" s="19" t="n"/>
+      <c r="J34" s="19" t="n"/>
+      <c r="K34" s="19" t="n"/>
+      <c r="L34" s="19" t="n"/>
+      <c r="M34" s="19" t="n"/>
+      <c r="N34" s="19" t="n"/>
+      <c r="O34" s="19" t="n"/>
+      <c r="P34" s="19" t="n"/>
+      <c r="Q34" s="19" t="n"/>
+      <c r="R34" s="19" t="n"/>
+      <c r="S34" s="20">
         <f>IF(B34="","",IF(C34="役員","対象外（役員）",IF(NOT(OR(C34="正社員",C34="契約社員",C34="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D34:O34)=12,COUNTIF(D34:O34,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C34="パート・アルバイト",N(R34)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D34:O34)-N(Q34)+N(P34)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T34" s="19">
+      <c r="T34" s="21">
         <f>IF(S34="集計対象",SUM(D34:O34)-N(Q34)+N(P34),"")</f>
         <v/>
       </c>
-      <c r="U34" s="20">
-        <f>IF(S34&lt;&gt;"集計対象",0,IF(OR(C34="正社員",C34="契約社員"),1,N(R34)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V34" s="21">
-        <f>IF(S34="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S34="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S34="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S34="集計対象",C34="パート・アルバイト",N(R34)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U34" s="22">
+        <f>IF(S34&lt;&gt;"集計対象",0,IF(OR(C34="正社員",C34="契約社員"),1,N(R34)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V34" s="23">
+        <f>IF(S34="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S34="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S34="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S34="集計対象",C34="パート・アルバイト",N(R34)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="n">
+      <c r="A35" s="16" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="17" t="n"/>
-      <c r="G35" s="17" t="n"/>
-      <c r="H35" s="17" t="n"/>
-      <c r="I35" s="17" t="n"/>
-      <c r="J35" s="17" t="n"/>
-      <c r="K35" s="17" t="n"/>
-      <c r="L35" s="17" t="n"/>
-      <c r="M35" s="17" t="n"/>
-      <c r="N35" s="17" t="n"/>
-      <c r="O35" s="17" t="n"/>
-      <c r="P35" s="17" t="n"/>
-      <c r="Q35" s="17" t="n"/>
-      <c r="R35" s="17" t="n"/>
-      <c r="S35" s="18">
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="19" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="19" t="n"/>
+      <c r="J35" s="19" t="n"/>
+      <c r="K35" s="19" t="n"/>
+      <c r="L35" s="19" t="n"/>
+      <c r="M35" s="19" t="n"/>
+      <c r="N35" s="19" t="n"/>
+      <c r="O35" s="19" t="n"/>
+      <c r="P35" s="19" t="n"/>
+      <c r="Q35" s="19" t="n"/>
+      <c r="R35" s="19" t="n"/>
+      <c r="S35" s="20">
         <f>IF(B35="","",IF(C35="役員","対象外（役員）",IF(NOT(OR(C35="正社員",C35="契約社員",C35="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D35:O35)=12,COUNTIF(D35:O35,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C35="パート・アルバイト",N(R35)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D35:O35)-N(Q35)+N(P35)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T35" s="19">
+      <c r="T35" s="21">
         <f>IF(S35="集計対象",SUM(D35:O35)-N(Q35)+N(P35),"")</f>
         <v/>
       </c>
-      <c r="U35" s="20">
-        <f>IF(S35&lt;&gt;"集計対象",0,IF(OR(C35="正社員",C35="契約社員"),1,N(R35)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V35" s="21">
-        <f>IF(S35="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S35="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S35="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S35="集計対象",C35="パート・アルバイト",N(R35)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U35" s="22">
+        <f>IF(S35&lt;&gt;"集計対象",0,IF(OR(C35="正社員",C35="契約社員"),1,N(R35)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V35" s="23">
+        <f>IF(S35="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S35="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S35="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S35="集計対象",C35="パート・アルバイト",N(R35)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n">
+      <c r="A36" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="17" t="n"/>
-      <c r="G36" s="17" t="n"/>
-      <c r="H36" s="17" t="n"/>
-      <c r="I36" s="17" t="n"/>
-      <c r="J36" s="17" t="n"/>
-      <c r="K36" s="17" t="n"/>
-      <c r="L36" s="17" t="n"/>
-      <c r="M36" s="17" t="n"/>
-      <c r="N36" s="17" t="n"/>
-      <c r="O36" s="17" t="n"/>
-      <c r="P36" s="17" t="n"/>
-      <c r="Q36" s="17" t="n"/>
-      <c r="R36" s="17" t="n"/>
-      <c r="S36" s="18">
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="19" t="n"/>
+      <c r="H36" s="19" t="n"/>
+      <c r="I36" s="19" t="n"/>
+      <c r="J36" s="19" t="n"/>
+      <c r="K36" s="19" t="n"/>
+      <c r="L36" s="19" t="n"/>
+      <c r="M36" s="19" t="n"/>
+      <c r="N36" s="19" t="n"/>
+      <c r="O36" s="19" t="n"/>
+      <c r="P36" s="19" t="n"/>
+      <c r="Q36" s="19" t="n"/>
+      <c r="R36" s="19" t="n"/>
+      <c r="S36" s="20">
         <f>IF(B36="","",IF(C36="役員","対象外（役員）",IF(NOT(OR(C36="正社員",C36="契約社員",C36="パート・アルバイト")),"要確認（雇用形態未選択）",IF(NOT(AND(COUNT(D36:O36)=12,COUNTIF(D36:O36,"&gt;0")=12)),"対象外（全月支給なし）",IF(AND(C36="パート・アルバイト",N(R36)&lt;=0),"要確認（労働時間未入力）",IF(SUM(D36:O36)-N(Q36)+N(P36)&lt;=0,"要確認（金額の確認）","集計対象"))))))</f>
         <v/>
       </c>
-      <c r="T36" s="19">
+      <c r="T36" s="21">
         <f>IF(S36="集計対象",SUM(D36:O36)-N(Q36)+N(P36),"")</f>
         <v/>
       </c>
-      <c r="U36" s="20">
-        <f>IF(S36&lt;&gt;"集計対象",0,IF(OR(C36="正社員",C36="契約社員"),1,N(R36)/$C$48))</f>
-        <v/>
-      </c>
-      <c r="V36" s="21">
-        <f>IF(S36="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S36="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S36="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S36="集計対象",C36="パート・アルバイト",N(R36)&gt;2080),"⚠年間労働時間が2080時間を超えています。桁をご確認ください",""))))</f>
+      <c r="U36" s="22">
+        <f>IF(S36&lt;&gt;"集計対象",0,IF(OR(C36="正社員",C36="契約社員"),1,N(R36)/IF(N($C$48)&gt;0,$C$48,2080)))</f>
+        <v/>
+      </c>
+      <c r="V36" s="23">
+        <f>IF(S36="要確認（雇用形態未選択）","⚠雇用形態をプルダウンから選択してください",IF(S36="要確認（労働時間未入力）","⚠パート・アルバイトは年間労働時間の入力が必要です",IF(S36="要確認（金額の確認）","⚠年間通勤手当が支給合計を上回っています。金額をご確認ください",IF(AND(S36="集計対象",C36="パート・アルバイト",N(R36)&gt;IF(N($C$48)&gt;0,$C$48,2080)),"⚠年間労働時間が正社員の年間所定労働時間を超えています。桁をご確認ください",""))))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>■ 会社全体の集計（自動計算 → 「提出用シート」に反映）</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+      <c r="A39" s="24" t="inlineStr">
         <is>
           <t>給与支給総額（R216）</t>
         </is>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="25">
         <f>SUM(T7:T36)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>従業員数（FTE換算・R215）</t>
         </is>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="26">
         <f>ROUND(SUM(U7:U36),1)</f>
         <v/>
       </c>
@@ -2375,7 +2391,7 @@
           <t xml:space="preserve">　内訳：フルタイム人数（正社員＋契約社員）</t>
         </is>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="27">
         <f>COUNTIFS($S$7:$S$36,"集計対象",$C$7:$C$36,"正社員")+COUNTIFS($S$7:$S$36,"集計対象",$C$7:$C$36,"契約社員")</f>
         <v/>
       </c>
@@ -2386,7 +2402,7 @@
           <t xml:space="preserve">　内訳：パート・アルバイト人数</t>
         </is>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="27">
         <f>COUNTIFS($S$7:$S$36,"集計対象",$C$7:$C$36,"パート・アルバイト")</f>
         <v/>
       </c>
@@ -2397,7 +2413,7 @@
           <t xml:space="preserve">　内訳：パート・アルバイト 年間労働時間 合計</t>
         </is>
       </c>
-      <c r="C43" s="19">
+      <c r="C43" s="21">
         <f>SUMIFS($R$7:$R$36,$S$7:$S$36,"集計対象",$C$7:$C$36,"パート・アルバイト")</f>
         <v/>
       </c>
@@ -2408,7 +2424,7 @@
           <t xml:space="preserve">　対象者 合計人数</t>
         </is>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="27">
         <f>COUNTIF($S$7:$S$36,"集計対象")</f>
         <v/>
       </c>
@@ -2419,7 +2435,7 @@
           <t xml:space="preserve">　参考：1人当たり給与支給総額（FTE換算1人当たり）</t>
         </is>
       </c>
-      <c r="C45" s="19">
+      <c r="C45" s="21">
         <f>IFERROR($C$39/$C$40,"")</f>
         <v/>
       </c>
@@ -2430,7 +2446,7 @@
           <t xml:space="preserve">　参考：時間欄に入力があった対象者の年間労働時間 合計</t>
         </is>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="28">
         <f>SUMIFS($R$7:$R$36,$S$7:$S$36,"集計対象")</f>
         <v/>
       </c>
@@ -2441,23 +2457,23 @@
           <t xml:space="preserve">　入力チェック：要確認・警告の件数（0 であること）</t>
         </is>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="29">
         <f>COUNTIF(V7:V36,"⚠*")+IF($A$4="",0,1)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>労働時間換算の分母（時間／年・固定）</t>
-        </is>
-      </c>
-      <c r="C48" s="28" t="n">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>正社員の年間所定労働時間（FTE換算の分母）</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="n">
         <v>2080</v>
       </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>※正社員の年間所定労働時間相当（週40h×52週）。変更しないでください。</t>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>※例：2080時間（週40h×52週）。自社の正社員フルタイムの所定労働時間に変更できます。パート人数の換算に使います。</t>
         </is>
       </c>
     </row>
@@ -2480,9 +2496,12 @@
     <mergeCell ref="A4:V4"/>
     <mergeCell ref="A39:B39"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="C7:C36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="一覧から選択してください" prompt="正社員／契約社員／パート・アルバイト／役員 から選択" type="list">
       <formula1>"正社員,契約社員,パート・アルバイト,役員"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C48" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="1以上の整数（例：2080）でご入力ください" prompt="正社員がフルタイムで1年間に働く所定労働時間（例：2080）" type="whole" operator="greaterThan">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2512,100 +2531,100 @@
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>会社名</t>
         </is>
       </c>
-      <c r="C2" s="15" t="n"/>
+      <c r="C2" s="17" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>記入日</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
+      <c r="C3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="B4" s="11">
+      <c r="B4" s="13">
         <f>IF('計算用（社内控え・非提出）'!$C$47=0,"","⚠ 計算用シートに未解消の要確認・警告が "&amp;'計算用（社内控え・非提出）'!$C$47&amp;" 件あります。解消してからご提出ください。")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
         <is>
           <t>対象期間（前期決算期・12ヶ月）</t>
         </is>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>IF(OR('計算用（社内控え・非提出）'!D3="",'計算用（社内控え・非提出）'!F3=""),"（未入力）計算用シートに対象期間をご記入ください",TEXT('計算用（社内控え・非提出）'!D3,"yyyy年m月d日")&amp;" 〜 "&amp;TEXT('計算用（社内控え・非提出）'!F3,"yyyy年m月d日"))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>給与支給総額（R216）</t>
         </is>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <f>'計算用（社内控え・非提出）'!C39</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>従業員数（FTE換算・R215）</t>
         </is>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="35">
         <f>'計算用（社内控え・非提出）'!C40</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">　内訳：フルタイム人数（正社員＋契約社員）</t>
         </is>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="36">
         <f>'計算用（社内控え・非提出）'!C41</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">　内訳：パート・アルバイト人数</t>
         </is>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="36">
         <f>'計算用（社内控え・非提出）'!C42</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">　内訳：パート・アルバイト 年間労働時間 合計</t>
         </is>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>'計算用（社内控え・非提出）'!C43</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">　参考：1人当たり給与支給総額（FTE換算1人当たり）</t>
         </is>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="37">
         <f>'計算用（社内控え・非提出）'!C45</f>
         <v/>
       </c>

--- a/ツール/賃金台帳（総額提出用）テンプレート.xlsx
+++ b/ツール/賃金台帳（総額提出用）テンプレート.xlsx
@@ -758,14 +758,14 @@
     <row r="22">
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>・給与ソフト等で各月の「課税支給合計（課税計）」が分かる場合は、そちらの方が正確です。</t>
+          <t>・「課税支給合計（課税計）」ではなく「総支給額」でお願いします（通勤手当を含む金額）。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　その場合は「年間通勤手当」欄を空欄にしてください（二重に差し引かないため）。</t>
+          <t xml:space="preserve">　通勤手当は「年間通勤手当」欄にご記入いただいた金額でこちらが差し引きます。</t>
         </is>
       </c>
     </row>
@@ -820,35 +820,35 @@
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>【年間通勤手当（非課税分）】</t>
+          <t>【年間通勤手当】</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>・毎月の欄に通勤手当を含めた場合は、非課税分の年間合計を必ずご記入ください。</t>
+          <t>・毎月の欄に通勤手当を含めた場合は、通勤手当の年間合計を必ずご記入ください。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　（補助金のルールで非課税の通勤手当は集計から除く決まりです。空欄のままだと</t>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　課税・非課税の区別は不要です（どちらも集計から除きます）。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　総額が過大になり、賃上げ目標が実態より高く設定されてしまいます。金額は</t>
+          <t xml:space="preserve">　（空欄のままだと総額が過大になり、賃上げ目標が実態より高く設定されてしまいます。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　給与ソフトの「非課税支給額」や賃金台帳の通勤手当欄でご確認いただけます）</t>
+          <t xml:space="preserve">　金額は給与ソフトの通勤手当欄・賃金台帳の通勤手当の行でご確認いただけます）</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       <c r="Q6" s="15" t="inlineStr">
         <is>
           <t>年間通勤手当
-(非課税分)</t>
+(全額)</t>
         </is>
       </c>
       <c r="R6" s="15" t="inlineStr">
